--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.100.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.100.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.100.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.100.xlsx
@@ -423,21 +423,21 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -603,14 +603,22 @@
       </c>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L131: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: he ends of justice ； and, when any</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]93</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]93</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L40: symbol-only separator/garbage line :: 1850.</t>
@@ -618,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L22: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "other party to" vs "1850 LXXX Considering" :: 1850.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]93</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -628,7 +636,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • itself.</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -665,7 +677,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the said decree or orderâ€žand shall serve the same upon the</t>
+          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to proceed to the hearing and determining of such refer-€</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: V</t>
+          <t>L22: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "other party to" vs "1850 LXXX Considering" :: 1850.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -716,7 +728,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: to proceed to the hearing and determining of such refer-â‚¬</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • itself.</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -726,7 +738,11 @@
           <t>L137: isolated marker/symbol line :: 0</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L56: isolated marker/symbol line :: V</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -746,12 +762,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -761,11 +777,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ itself.</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
@@ -945,12 +957,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -989,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1028,7 +1040,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1106,7 +1118,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
